--- a/MarketDashboard/sector_etf_stock_list.xlsx
+++ b/MarketDashboard/sector_etf_stock_list.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27.68669793078719</v>
+        <v>27.41584230793897</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1049490396854984</v>
+        <v>0.08996989228604989</v>
       </c>
     </row>
     <row r="3">
@@ -510,26 +510,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24.54552649898897</v>
+        <v>24.46770236586592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05023836907990932</v>
+        <v>0.02034190053487548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>通訊</t>
+          <t>軟件SaaS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Software &amp; Saas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -538,26 +538,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18.60838962557314</v>
+        <v>27.00795317501059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08158236238261883</v>
+        <v>-0.01411765301194951</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>消費</t>
+          <t>半導體</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Consumerdisc</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -566,26 +566,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24.40968956613633</v>
+        <v>39.86171839096934</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04047343490168833</v>
+        <v>0.1897731928628345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>房屋建築商</t>
+          <t>通訊</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Home Builders</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -594,26 +594,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28.31423358390401</v>
+        <v>18.46532355474204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01169888486214589</v>
+        <v>0.07453034081961438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>消費</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Consumerdisc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,26 +622,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25.11319978683568</v>
+        <v>24.26049046974937</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0516218172684075</v>
+        <v>0.0404626459652624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>消費必需品</t>
+          <t>房屋建築商</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Home Builders</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -650,26 +650,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13.87150765140455</v>
+        <v>28.89143476252919</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007103533565130793</v>
+        <v>0.02688363514894025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -678,26 +678,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24.54668756235936</v>
+        <v>25.28968500903622</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0445915302366075</v>
+        <v>0.06571736786156297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>油氣勘探者</t>
+          <t>消費必需品</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oil&amp; Gas Explorator</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -706,26 +706,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32.85782959503482</v>
+        <v>14.09621195943499</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02658723661104913</v>
+        <v>0.03990874425805214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>石油服務</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Oil Service</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -734,26 +734,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36.84227092432074</v>
+        <v>25.10284337987684</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06269722053749163</v>
+        <v>0.05110681888967437</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>太陽能</t>
+          <t>油氣勘探者</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Oil&amp; Gas Explorator</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,26 +762,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>38.28584888525492</v>
+        <v>33.23238826759872</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1820802021488931</v>
+        <v>0.009409813771941928</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>核能</t>
+          <t>石油服務</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Oil Service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -790,26 +790,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45.56746942054162</v>
+        <v>37.65594033793867</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2514355357353964</v>
+        <v>0.09896882492068906</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>太陽能</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19.08908687186689</v>
+        <v>38.06125703035954</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06921870837731986</v>
+        <v>0.2303506528980612</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>核能</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -846,26 +846,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25.93615162829173</v>
+        <v>46.03693469041526</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0737006262692862</v>
+        <v>0.3086299423601584</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>保險</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KIE</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -874,26 +874,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19.8569270708176</v>
+        <v>19.05429061867212</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0494233444914288</v>
+        <v>0.03871896893872594</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>衛生保健</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -902,26 +902,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>17.35505606984442</v>
+        <v>25.84428361075152</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06113444476914565</v>
+        <v>0.06859901961143054</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>生物技術</t>
+          <t>保險</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>KIE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -930,26 +930,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>22.76366376549701</v>
+        <v>19.63394223168689</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1116277877779333</v>
+        <v>0.02425066163023743</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>醫療設備</t>
+          <t>衛生保健</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -958,26 +958,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18.67798570834753</v>
+        <v>17.33731021279583</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03943130713168029</v>
+        <v>0.05567717518549193</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>工業</t>
+          <t>生物技術</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -986,26 +986,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>18.8528865804856</v>
+        <v>23.12454364943328</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07796623124576668</v>
+        <v>0.1172247911157191</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>航空與國防</t>
+          <t>醫療設備</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aero &amp; National Defence</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21.61211483322304</v>
+        <v>18.67175466762128</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1722463446745079</v>
+        <v>-0.007597414031089627</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>運輸</t>
+          <t>工業</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1042,26 +1042,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>25.18479445722323</v>
+        <v>19.06618535686715</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0585044156768454</v>
+        <v>0.07857254549983879</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>航空與國防</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Aero &amp; National Defence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1070,26 +1070,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20.06557815892415</v>
+        <v>22.22643309316146</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03973219709601519</v>
+        <v>0.1781275330703954</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>黃金礦探</t>
+          <t>運輸</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1098,26 +1098,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>36.96104597172764</v>
+        <v>25.4622130740001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4042593485991005</v>
+        <v>0.05058341967574132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>金屬與採礦</t>
+          <t>噴氣機</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Metals&amp;Mining</t>
+          <t>Jets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>32.24870773597706</v>
+        <v>36.48859938477288</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2615650491722651</v>
+        <v>0.06364415271143874</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>鋰電池</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lithium&amp;Battery</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1154,26 +1154,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31.61438794138021</v>
+        <v>20.24047161806568</v>
       </c>
       <c r="F26" t="n">
-        <v>0.191075152871691</v>
+        <v>0.05967749145634246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>基礎材料</t>
+          <t>黃金礦探</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IYM</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1182,38 +1182,178 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20.68608593974828</v>
+        <v>38.16003064758174</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07790413358507921</v>
+        <v>0.443198781931211</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>金屬與採礦</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Metals&amp;Mining</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>XME</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Vanguard Real Estate Index Fund ETF</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>32.99401782013341</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3312878081427034</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>鋰電池</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lithium&amp;Battery</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LIT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Vanguard Real Estate Index Fund ETF</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>32.05356681406952</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.2492368429584463</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>基礎材料</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IYM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Vanguard Real Estate Index Fund ETF</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20.90968142573656</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1077852484686543</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>房地產</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>XLRE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Vanguard Real Estate Index Fund ETF</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>16.42496653495962</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.01921386214006306</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>房地產信託</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Reit Us</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>VNQ</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Vanguard Real Estate Index Fund ETF</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>17.18085243549448</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.01855652101631582</v>
+      <c r="E32" t="n">
+        <v>16.55081355602642</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.02353127156807609</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>公用事業</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vanguard Real Estate Index Fund ETF</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>15.72147390873957</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.05070834465857221</v>
       </c>
     </row>
   </sheetData>
